--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:25:22+00:00</t>
+    <t>2025-07-07T15:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:26:46+00:00</t>
+    <t>2025-10-08T07:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -484,10 +484,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -502,16 +502,10 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -865,7 +859,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="38.39453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="46.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -879,8 +873,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="37.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.34765625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="27.484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2074,13 +2068,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2113,10 +2107,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2124,10 +2118,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2150,17 +2144,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2209,7 +2203,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2224,13 +2218,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:41:56+00:00</t>
+    <t>2025-10-08T15:42:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
